--- a/DATA/06_deposit_composition.xlsx
+++ b/DATA/06_deposit_composition.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,31 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,44 +491,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2020</v>
       </c>
       <c r="D2" t="n">
-        <v>13500.7</v>
+        <v>12467</v>
       </c>
       <c r="E2" t="n">
-        <v>37801.9</v>
+        <v>38593</v>
       </c>
       <c r="F2" t="n">
-        <v>67503.39999999999</v>
+        <v>81839.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10800.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5400.3</v>
-      </c>
+        <v>10729.1</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>135006.8</v>
+        <v>143628.52</v>
       </c>
       <c r="J2" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -575,51 +532,47 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2021</v>
       </c>
       <c r="D3" t="n">
-        <v>17324.6</v>
+        <v>14132.3</v>
       </c>
       <c r="E3" t="n">
-        <v>48508.9</v>
+        <v>43748.4</v>
       </c>
       <c r="F3" t="n">
-        <v>86623.10000000001</v>
+        <v>92771.89999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>13859.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6929.8</v>
-      </c>
+        <v>12162.3</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>173246.1</v>
+        <v>162814.93</v>
       </c>
       <c r="J3" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -627,51 +580,47 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2022</v>
       </c>
       <c r="D4" t="n">
-        <v>20445</v>
+        <v>14460</v>
       </c>
       <c r="E4" t="n">
-        <v>57245.9</v>
+        <v>44762.8</v>
       </c>
       <c r="F4" t="n">
-        <v>102224.9</v>
+        <v>94923.10000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>16356</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8178</v>
-      </c>
+        <v>12444.3</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>204449.8</v>
+        <v>166590.27</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -679,51 +628,47 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2023</v>
       </c>
       <c r="D5" t="n">
-        <v>22998.9</v>
+        <v>12767.1</v>
       </c>
       <c r="E5" t="n">
-        <v>64397</v>
+        <v>60723.7</v>
       </c>
       <c r="F5" t="n">
-        <v>114994.7</v>
+        <v>110116.6</v>
       </c>
       <c r="G5" t="n">
-        <v>18399.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9199.6</v>
-      </c>
+        <v>15879.1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>229989.4</v>
+        <v>199486.61</v>
       </c>
       <c r="J5" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -731,51 +676,47 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2024</v>
       </c>
       <c r="D6" t="n">
-        <v>25151.7</v>
+        <v>18954.3</v>
       </c>
       <c r="E6" t="n">
-        <v>70424.8</v>
+        <v>89070.60000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>125758.5</v>
+        <v>115942.9</v>
       </c>
       <c r="G6" t="n">
-        <v>20121.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10060.6</v>
-      </c>
+        <v>19685.2</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>251517</v>
+        <v>243628.66</v>
       </c>
       <c r="J6" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.4</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -783,51 +724,47 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2025</v>
       </c>
       <c r="D7" t="n">
-        <v>26326.5</v>
+        <v>22823.3</v>
       </c>
       <c r="E7" t="n">
-        <v>73714.3</v>
+        <v>107252</v>
       </c>
       <c r="F7" t="n">
-        <v>131632.7</v>
+        <v>139609.5</v>
       </c>
       <c r="G7" t="n">
-        <v>21061.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10530.7</v>
-      </c>
+        <v>23703.4</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>263265.4</v>
+        <v>293358.98</v>
       </c>
       <c r="J7" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.4</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -835,51 +772,47 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>BOKL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Bank of Kathmandu</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2020</v>
       </c>
       <c r="D8" t="n">
-        <v>17506.2</v>
+        <v>7994.6</v>
       </c>
       <c r="E8" t="n">
-        <v>49017.3</v>
+        <v>24748.2</v>
       </c>
       <c r="F8" t="n">
-        <v>87530.89999999999</v>
+        <v>52480.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14004.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7002.5</v>
-      </c>
+        <v>6880.1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>175061.8</v>
+        <v>92103.3</v>
       </c>
       <c r="J8" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -887,51 +820,47 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>BOKL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Bank of Kathmandu</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2021</v>
       </c>
       <c r="D9" t="n">
-        <v>21319.6</v>
+        <v>8976.299999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>59694.9</v>
+        <v>27787.2</v>
       </c>
       <c r="F9" t="n">
-        <v>106597.9</v>
+        <v>58925</v>
       </c>
       <c r="G9" t="n">
-        <v>17055.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8527.799999999999</v>
-      </c>
+        <v>7725</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>213195.9</v>
+        <v>103413.43</v>
       </c>
       <c r="J9" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -939,51 +868,47 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>CCBL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Century Commercial Bank</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D10" t="n">
-        <v>26168.1</v>
+        <v>5669.3</v>
       </c>
       <c r="E10" t="n">
-        <v>73270.60000000001</v>
+        <v>17550.1</v>
       </c>
       <c r="F10" t="n">
-        <v>130840.4</v>
+        <v>37216.4</v>
       </c>
       <c r="G10" t="n">
-        <v>20934.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10467.1</v>
-      </c>
+        <v>4879</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>261680.7</v>
+        <v>65314.89</v>
       </c>
       <c r="J10" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -991,51 +916,47 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>CCBL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Century Commercial Bank</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D11" t="n">
-        <v>29743.6</v>
+        <v>8115.5</v>
       </c>
       <c r="E11" t="n">
-        <v>83282</v>
+        <v>25122.5</v>
       </c>
       <c r="F11" t="n">
-        <v>148717.8</v>
+        <v>53274.4</v>
       </c>
       <c r="G11" t="n">
-        <v>23794.8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11897.4</v>
-      </c>
+        <v>6984.2</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>297435.6</v>
+        <v>93496.63</v>
       </c>
       <c r="J11" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K11" t="n">
-        <v>50</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1043,51 +964,47 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>CIVIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Civil Bank</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D12" t="n">
-        <v>31729.2</v>
+        <v>4992.1</v>
       </c>
       <c r="E12" t="n">
-        <v>88841.7</v>
+        <v>15453.6</v>
       </c>
       <c r="F12" t="n">
-        <v>158645.9</v>
+        <v>32770.6</v>
       </c>
       <c r="G12" t="n">
-        <v>25383.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>12691.6</v>
-      </c>
+        <v>4296.2</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>317291.7</v>
+        <v>57512.41</v>
       </c>
       <c r="J12" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1095,51 +1012,47 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>CIVIL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Civil Bank</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D13" t="n">
-        <v>33996</v>
+        <v>7693.5</v>
       </c>
       <c r="E13" t="n">
-        <v>95188.7</v>
+        <v>23816.2</v>
       </c>
       <c r="F13" t="n">
-        <v>169979.9</v>
+        <v>50504.2</v>
       </c>
       <c r="G13" t="n">
-        <v>27196.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>13598.3</v>
-      </c>
+        <v>6621</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>339959.7</v>
+        <v>88634.88</v>
       </c>
       <c r="J13" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1147,51 +1060,47 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2020</v>
       </c>
       <c r="D14" t="n">
-        <v>12676.8</v>
+        <v>12459.7</v>
       </c>
       <c r="E14" t="n">
-        <v>35495</v>
+        <v>38570.7</v>
       </c>
       <c r="F14" t="n">
-        <v>63383.9</v>
+        <v>81792.2</v>
       </c>
       <c r="G14" t="n">
-        <v>10141.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5070.8</v>
-      </c>
+        <v>10722.8</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>126767.9</v>
+        <v>143545.48</v>
       </c>
       <c r="J14" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.2</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1199,51 +1108,47 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2021</v>
       </c>
       <c r="D15" t="n">
-        <v>15754.6</v>
+        <v>12207.4</v>
       </c>
       <c r="E15" t="n">
-        <v>44112.9</v>
+        <v>37789.5</v>
       </c>
       <c r="F15" t="n">
-        <v>78773</v>
+        <v>80135.8</v>
       </c>
       <c r="G15" t="n">
-        <v>12603.7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6301.8</v>
-      </c>
+        <v>10505.7</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>157546</v>
+        <v>140638.41</v>
       </c>
       <c r="J15" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.2</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1251,51 +1156,47 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2022</v>
       </c>
       <c r="D16" t="n">
-        <v>18321.8</v>
+        <v>13263.2</v>
       </c>
       <c r="E16" t="n">
-        <v>51301.2</v>
+        <v>41057.8</v>
       </c>
       <c r="F16" t="n">
-        <v>91609.2</v>
+        <v>87066.3</v>
       </c>
       <c r="G16" t="n">
-        <v>14657.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>7328.7</v>
-      </c>
+        <v>11414.3</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>183218.4</v>
+        <v>152801.49</v>
       </c>
       <c r="J16" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
-      </c>
-      <c r="L16" t="n">
-        <v>8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1303,51 +1204,47 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2023</v>
       </c>
       <c r="D17" t="n">
-        <v>19815.6</v>
+        <v>10805.9</v>
       </c>
       <c r="E17" t="n">
-        <v>55483.7</v>
+        <v>51395.5</v>
       </c>
       <c r="F17" t="n">
-        <v>99078</v>
+        <v>93200.89999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>15852.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7926.2</v>
-      </c>
+        <v>13439.8</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>198156</v>
+        <v>168842.14</v>
       </c>
       <c r="J17" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1355,51 +1252,47 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2024</v>
       </c>
       <c r="D18" t="n">
-        <v>22247</v>
+        <v>14722.6</v>
       </c>
       <c r="E18" t="n">
-        <v>62291.5</v>
+        <v>69184.89999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>111234.9</v>
+        <v>90057.7</v>
       </c>
       <c r="G18" t="n">
-        <v>17797.6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>8898.799999999999</v>
-      </c>
+        <v>15290.3</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>222469.8</v>
+        <v>189236.67</v>
       </c>
       <c r="J18" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.2</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1407,51 +1300,47 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2025</v>
       </c>
       <c r="D19" t="n">
-        <v>22897.8</v>
+        <v>16454.8</v>
       </c>
       <c r="E19" t="n">
-        <v>64113.9</v>
+        <v>77324.7</v>
       </c>
       <c r="F19" t="n">
-        <v>114489.1</v>
+        <v>100653.2</v>
       </c>
       <c r="G19" t="n">
-        <v>18318.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>9159.1</v>
-      </c>
+        <v>17089.3</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>228978.2</v>
+        <v>211500.79</v>
       </c>
       <c r="J19" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.2</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1459,51 +1348,47 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2020</v>
       </c>
       <c r="D20" t="n">
-        <v>23562</v>
+        <v>12459.7</v>
       </c>
       <c r="E20" t="n">
-        <v>65973.60000000001</v>
+        <v>38570.7</v>
       </c>
       <c r="F20" t="n">
-        <v>117810</v>
+        <v>81792.2</v>
       </c>
       <c r="G20" t="n">
-        <v>18849.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>9424.799999999999</v>
-      </c>
+        <v>10722.8</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>235620</v>
+        <v>143545.48</v>
       </c>
       <c r="J20" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K20" t="n">
-        <v>50</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5.7</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1511,51 +1396,47 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2021</v>
       </c>
       <c r="D21" t="n">
-        <v>28679.9</v>
+        <v>13907.1</v>
       </c>
       <c r="E21" t="n">
-        <v>80303.60000000001</v>
+        <v>43051.2</v>
       </c>
       <c r="F21" t="n">
-        <v>143399.2</v>
+        <v>91293.5</v>
       </c>
       <c r="G21" t="n">
-        <v>22943.9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>11471.9</v>
-      </c>
+        <v>11968.5</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>286798.5</v>
+        <v>160220.26</v>
       </c>
       <c r="J21" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K21" t="n">
-        <v>50</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5.7</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1563,51 +1444,47 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2022</v>
       </c>
       <c r="D22" t="n">
-        <v>34922.2</v>
+        <v>14993.8</v>
       </c>
       <c r="E22" t="n">
-        <v>97782.3</v>
+        <v>46415</v>
       </c>
       <c r="F22" t="n">
-        <v>174611.2</v>
+        <v>98426.8</v>
       </c>
       <c r="G22" t="n">
-        <v>27937.8</v>
-      </c>
-      <c r="H22" t="n">
-        <v>13969</v>
-      </c>
+        <v>12903.6</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>349222.5</v>
+        <v>172739.18</v>
       </c>
       <c r="J22" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1615,51 +1492,47 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2023</v>
       </c>
       <c r="D23" t="n">
-        <v>39790.2</v>
+        <v>12672.5</v>
       </c>
       <c r="E23" t="n">
-        <v>111412.6</v>
+        <v>60273.6</v>
       </c>
       <c r="F23" t="n">
-        <v>198951</v>
+        <v>109300.3</v>
       </c>
       <c r="G23" t="n">
-        <v>31832.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>15916</v>
-      </c>
+        <v>15761.4</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>397902</v>
+        <v>198007.81</v>
       </c>
       <c r="J23" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.5</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1667,51 +1540,47 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2024</v>
       </c>
       <c r="D24" t="n">
-        <v>42495.8</v>
+        <v>18074.2</v>
       </c>
       <c r="E24" t="n">
-        <v>118988.1</v>
+        <v>84934.89999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>212478.8</v>
+        <v>110559.5</v>
       </c>
       <c r="G24" t="n">
-        <v>33996.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>16998.2</v>
-      </c>
+        <v>18771.2</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>424957.5</v>
+        <v>232316.6</v>
       </c>
       <c r="J24" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K24" t="n">
-        <v>50</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5.7</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1719,51 +1588,47 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2025</v>
       </c>
       <c r="D25" t="n">
-        <v>45027.9</v>
+        <v>23248.1</v>
       </c>
       <c r="E25" t="n">
-        <v>126078.1</v>
+        <v>109248</v>
       </c>
       <c r="F25" t="n">
-        <v>225139.5</v>
+        <v>142207.7</v>
       </c>
       <c r="G25" t="n">
-        <v>36022.3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>18011.2</v>
-      </c>
+        <v>24144.5</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>450279</v>
+        <v>298818.4</v>
       </c>
       <c r="J25" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K25" t="n">
-        <v>50</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5.7</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1771,51 +1636,47 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2020</v>
       </c>
       <c r="D26" t="n">
-        <v>22747.5</v>
+        <v>18429</v>
       </c>
       <c r="E26" t="n">
-        <v>63693</v>
+        <v>57049.1</v>
       </c>
       <c r="F26" t="n">
-        <v>113737.4</v>
+        <v>120977.3</v>
       </c>
       <c r="G26" t="n">
-        <v>18198</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9099</v>
-      </c>
+        <v>15860</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>227474.9</v>
+        <v>212315.39</v>
       </c>
       <c r="J26" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.2</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1823,51 +1684,47 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2021</v>
       </c>
       <c r="D27" t="n">
-        <v>26869.4</v>
+        <v>23300.1</v>
       </c>
       <c r="E27" t="n">
-        <v>75234.2</v>
+        <v>72128.2</v>
       </c>
       <c r="F27" t="n">
-        <v>134346.8</v>
+        <v>152953.6</v>
       </c>
       <c r="G27" t="n">
-        <v>21495.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>10747.6</v>
-      </c>
+        <v>20052</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>268693.5</v>
+        <v>268433.79</v>
       </c>
       <c r="J27" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.2</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1875,51 +1732,47 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2022</v>
       </c>
       <c r="D28" t="n">
-        <v>31361.2</v>
+        <v>24040.6</v>
       </c>
       <c r="E28" t="n">
-        <v>87811.3</v>
+        <v>74420.5</v>
       </c>
       <c r="F28" t="n">
-        <v>156805.9</v>
+        <v>157814.6</v>
       </c>
       <c r="G28" t="n">
-        <v>25088.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>12544.5</v>
-      </c>
+        <v>20689.3</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>313611.8</v>
+        <v>276964.91</v>
       </c>
       <c r="J28" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K28" t="n">
-        <v>50</v>
-      </c>
-      <c r="L28" t="n">
-        <v>8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1927,51 +1780,47 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2023</v>
       </c>
       <c r="D29" t="n">
-        <v>36449.7</v>
+        <v>27284.8</v>
       </c>
       <c r="E29" t="n">
-        <v>102059.2</v>
+        <v>129773.5</v>
       </c>
       <c r="F29" t="n">
-        <v>182248.5</v>
+        <v>235331.6</v>
       </c>
       <c r="G29" t="n">
-        <v>29159.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>14579.8</v>
-      </c>
+        <v>33935.5</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>364497</v>
+        <v>426325.45</v>
       </c>
       <c r="J29" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
-      </c>
-      <c r="L29" t="n">
-        <v>8</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -1979,51 +1828,47 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2024</v>
       </c>
       <c r="D30" t="n">
-        <v>37557.7</v>
+        <v>37924.1</v>
       </c>
       <c r="E30" t="n">
-        <v>105161.5</v>
+        <v>178213.9</v>
       </c>
       <c r="F30" t="n">
-        <v>187788.4</v>
+        <v>231980.2</v>
       </c>
       <c r="G30" t="n">
-        <v>30046.1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>15023.1</v>
-      </c>
+        <v>39386.4</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>375576.8</v>
+        <v>487455.85</v>
       </c>
       <c r="J30" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K30" t="n">
-        <v>50</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.2</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2031,51 +1876,47 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2025</v>
       </c>
       <c r="D31" t="n">
-        <v>42053.5</v>
+        <v>42838.9</v>
       </c>
       <c r="E31" t="n">
-        <v>117749.9</v>
+        <v>201309.8</v>
       </c>
       <c r="F31" t="n">
-        <v>210267.7</v>
+        <v>262044.1</v>
       </c>
       <c r="G31" t="n">
-        <v>33642.8</v>
-      </c>
-      <c r="H31" t="n">
-        <v>16821.5</v>
-      </c>
+        <v>44490.8</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>420535.4</v>
+        <v>550628.59</v>
       </c>
       <c r="J31" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.2</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2083,51 +1924,47 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2020</v>
       </c>
       <c r="D32" t="n">
-        <v>6263.6</v>
+        <v>10872.9</v>
       </c>
       <c r="E32" t="n">
-        <v>17538</v>
+        <v>33658.5</v>
       </c>
       <c r="F32" t="n">
-        <v>31317.8</v>
+        <v>71375.60000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>5010.8</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2505.4</v>
-      </c>
+        <v>9357.200000000001</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>62635.6</v>
+        <v>125264.38</v>
       </c>
       <c r="J32" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K32" t="n">
-        <v>50</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5.8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2135,51 +1972,47 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2021</v>
       </c>
       <c r="D33" t="n">
-        <v>7501.1</v>
+        <v>12240.6</v>
       </c>
       <c r="E33" t="n">
-        <v>21003.1</v>
+        <v>37892.4</v>
       </c>
       <c r="F33" t="n">
-        <v>37505.6</v>
+        <v>80353.8</v>
       </c>
       <c r="G33" t="n">
-        <v>6000.9</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3000.5</v>
-      </c>
+        <v>10534.3</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>75011.2</v>
+        <v>141021.07</v>
       </c>
       <c r="J33" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
-      </c>
-      <c r="L33" t="n">
-        <v>5.8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2187,51 +2020,47 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>2022</v>
       </c>
       <c r="D34" t="n">
-        <v>8953.6</v>
+        <v>14618.8</v>
       </c>
       <c r="E34" t="n">
-        <v>25070.2</v>
+        <v>45254.3</v>
       </c>
       <c r="F34" t="n">
-        <v>44768.2</v>
+        <v>95965.39999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>7162.9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3581.4</v>
-      </c>
+        <v>12580.9</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>89536.3</v>
+        <v>168419.49</v>
       </c>
       <c r="J34" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K34" t="n">
-        <v>50</v>
-      </c>
-      <c r="L34" t="n">
-        <v>7.6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2239,51 +2068,47 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2023</v>
       </c>
       <c r="D35" t="n">
-        <v>10034.1</v>
+        <v>17619.9</v>
       </c>
       <c r="E35" t="n">
-        <v>28095.4</v>
+        <v>83804.7</v>
       </c>
       <c r="F35" t="n">
-        <v>50170.3</v>
+        <v>151971.7</v>
       </c>
       <c r="G35" t="n">
-        <v>8027.2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4013.6</v>
-      </c>
+        <v>21914.8</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>100340.6</v>
+        <v>275310.99</v>
       </c>
       <c r="J35" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K35" t="n">
-        <v>50</v>
-      </c>
-      <c r="L35" t="n">
-        <v>7.6</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2291,51 +2116,47 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2024</v>
       </c>
       <c r="D36" t="n">
-        <v>10951.5</v>
+        <v>22865.4</v>
       </c>
       <c r="E36" t="n">
-        <v>30664.2</v>
+        <v>107449.7</v>
       </c>
       <c r="F36" t="n">
-        <v>54757.5</v>
+        <v>139866.8</v>
       </c>
       <c r="G36" t="n">
-        <v>8761.200000000001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4380.6</v>
-      </c>
+        <v>23747.1</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>109515</v>
+        <v>293899.59</v>
       </c>
       <c r="J36" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K36" t="n">
-        <v>50</v>
-      </c>
-      <c r="L36" t="n">
-        <v>5.8</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2343,51 +2164,47 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2025</v>
       </c>
       <c r="D37" t="n">
-        <v>11440.6</v>
+        <v>24052.5</v>
       </c>
       <c r="E37" t="n">
-        <v>32033.6</v>
+        <v>113028.4</v>
       </c>
       <c r="F37" t="n">
-        <v>57202.8</v>
+        <v>147128.6</v>
       </c>
       <c r="G37" t="n">
-        <v>9152.4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4576.2</v>
-      </c>
+        <v>24980</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>114405.6</v>
+        <v>309158.67</v>
       </c>
       <c r="J37" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
-      </c>
-      <c r="L37" t="n">
-        <v>5.8</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2395,51 +2212,47 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2020</v>
       </c>
       <c r="D38" t="n">
-        <v>15757.6</v>
+        <v>10116.3</v>
       </c>
       <c r="E38" t="n">
-        <v>44121.2</v>
+        <v>31316.2</v>
       </c>
       <c r="F38" t="n">
-        <v>78787.8</v>
+        <v>66408.5</v>
       </c>
       <c r="G38" t="n">
-        <v>12606</v>
-      </c>
-      <c r="H38" t="n">
-        <v>6303</v>
-      </c>
+        <v>8706.1</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>157575.6</v>
+        <v>116547.03</v>
       </c>
       <c r="J38" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K38" t="n">
-        <v>50</v>
-      </c>
-      <c r="L38" t="n">
-        <v>6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2447,51 +2260,47 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2021</v>
       </c>
       <c r="D39" t="n">
-        <v>18194.4</v>
+        <v>12658.8</v>
       </c>
       <c r="E39" t="n">
-        <v>50944.3</v>
+        <v>39186.7</v>
       </c>
       <c r="F39" t="n">
-        <v>90972</v>
+        <v>83098.60000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>14555.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>7277.8</v>
-      </c>
+        <v>10894.1</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>181944</v>
+        <v>145838.23</v>
       </c>
       <c r="J39" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
-      </c>
-      <c r="L39" t="n">
-        <v>6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2499,51 +2308,47 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2022</v>
       </c>
       <c r="D40" t="n">
-        <v>22129.7</v>
+        <v>15343.4</v>
       </c>
       <c r="E40" t="n">
-        <v>61963.2</v>
+        <v>47497.5</v>
       </c>
       <c r="F40" t="n">
-        <v>110648.5</v>
+        <v>100722.2</v>
       </c>
       <c r="G40" t="n">
-        <v>17703.8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>8851.799999999999</v>
-      </c>
+        <v>13204.5</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>221297</v>
+        <v>176767.67</v>
       </c>
       <c r="J40" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K40" t="n">
-        <v>50</v>
-      </c>
-      <c r="L40" t="n">
-        <v>7.8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2551,51 +2356,47 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2023</v>
       </c>
       <c r="D41" t="n">
-        <v>24494.4</v>
+        <v>20227</v>
       </c>
       <c r="E41" t="n">
-        <v>68584.3</v>
+        <v>96204.7</v>
       </c>
       <c r="F41" t="n">
-        <v>122472</v>
+        <v>174458</v>
       </c>
       <c r="G41" t="n">
-        <v>19595.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>9797.799999999999</v>
-      </c>
+        <v>25157.3</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>244944</v>
+        <v>316047.05</v>
       </c>
       <c r="J41" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K41" t="n">
-        <v>50</v>
-      </c>
-      <c r="L41" t="n">
-        <v>7.8</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2603,51 +2404,47 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2024</v>
       </c>
       <c r="D42" t="n">
-        <v>26586.6</v>
+        <v>25916.1</v>
       </c>
       <c r="E42" t="n">
-        <v>74442.60000000001</v>
+        <v>121785.5</v>
       </c>
       <c r="F42" t="n">
-        <v>132933.1</v>
+        <v>158527.7</v>
       </c>
       <c r="G42" t="n">
-        <v>21269.3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>10634.7</v>
-      </c>
+        <v>26915.4</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>265866.3</v>
+        <v>333111.32</v>
       </c>
       <c r="J42" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K42" t="n">
-        <v>50</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2655,51 +2452,47 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2025</v>
       </c>
       <c r="D43" t="n">
-        <v>28451.1</v>
+        <v>28368.9</v>
       </c>
       <c r="E43" t="n">
-        <v>79663.10000000001</v>
+        <v>133312.1</v>
       </c>
       <c r="F43" t="n">
-        <v>142255.6</v>
+        <v>173531.8</v>
       </c>
       <c r="G43" t="n">
-        <v>22760.9</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11380.5</v>
-      </c>
+        <v>29462.8</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>284511.2</v>
+        <v>364639.16</v>
       </c>
       <c r="J43" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K43" t="n">
-        <v>50</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2707,51 +2500,47 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2020</v>
       </c>
       <c r="D44" t="n">
-        <v>8971.200000000001</v>
+        <v>8538.6</v>
       </c>
       <c r="E44" t="n">
-        <v>25119.5</v>
+        <v>26432.2</v>
       </c>
       <c r="F44" t="n">
-        <v>44856.2</v>
+        <v>56051.7</v>
       </c>
       <c r="G44" t="n">
-        <v>7177</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3588.5</v>
-      </c>
+        <v>7348.3</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>89712.39999999999</v>
+        <v>98370.75999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K44" t="n">
-        <v>50</v>
-      </c>
-      <c r="L44" t="n">
-        <v>5.8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2759,51 +2548,47 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2021</v>
       </c>
       <c r="D45" t="n">
-        <v>10557.5</v>
+        <v>9947.799999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>29561</v>
+        <v>30794.5</v>
       </c>
       <c r="F45" t="n">
-        <v>52787.6</v>
+        <v>65302.2</v>
       </c>
       <c r="G45" t="n">
-        <v>8446</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4223</v>
-      </c>
+        <v>8561</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>105575.1</v>
+        <v>114605.49</v>
       </c>
       <c r="J45" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K45" t="n">
-        <v>50</v>
-      </c>
-      <c r="L45" t="n">
-        <v>5.8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2811,51 +2596,47 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>2022</v>
       </c>
       <c r="D46" t="n">
-        <v>12880.6</v>
+        <v>12111.8</v>
       </c>
       <c r="E46" t="n">
-        <v>36065.6</v>
+        <v>37493.6</v>
       </c>
       <c r="F46" t="n">
-        <v>64402.8</v>
+        <v>79508.2</v>
       </c>
       <c r="G46" t="n">
-        <v>10304.4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>5152.2</v>
-      </c>
+        <v>10423.4</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>128805.6</v>
+        <v>139537.1</v>
       </c>
       <c r="J46" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K46" t="n">
-        <v>50</v>
-      </c>
-      <c r="L46" t="n">
-        <v>7.6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2863,51 +2644,47 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2023</v>
       </c>
       <c r="D47" t="n">
-        <v>14451.4</v>
+        <v>18959.6</v>
       </c>
       <c r="E47" t="n">
-        <v>40463.8</v>
+        <v>90176.5</v>
       </c>
       <c r="F47" t="n">
-        <v>72256.8</v>
+        <v>163526.4</v>
       </c>
       <c r="G47" t="n">
-        <v>11561.1</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5780.5</v>
-      </c>
+        <v>23581</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>144513.6</v>
+        <v>296243.48</v>
       </c>
       <c r="J47" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K47" t="n">
-        <v>50</v>
-      </c>
-      <c r="L47" t="n">
-        <v>7.6</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2915,51 +2692,47 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2024</v>
       </c>
       <c r="D48" t="n">
-        <v>15359</v>
+        <v>25590.9</v>
       </c>
       <c r="E48" t="n">
-        <v>43005.2</v>
+        <v>120257.4</v>
       </c>
       <c r="F48" t="n">
-        <v>76794.89999999999</v>
+        <v>156538.5</v>
       </c>
       <c r="G48" t="n">
-        <v>12287.2</v>
-      </c>
-      <c r="H48" t="n">
-        <v>6143.6</v>
-      </c>
+        <v>26577.7</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>153589.9</v>
+        <v>328931.51</v>
       </c>
       <c r="J48" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K48" t="n">
-        <v>50</v>
-      </c>
-      <c r="L48" t="n">
-        <v>5.8</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -2967,51 +2740,47 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2025</v>
       </c>
       <c r="D49" t="n">
-        <v>16099.5</v>
+        <v>28556.8</v>
       </c>
       <c r="E49" t="n">
-        <v>45078.6</v>
+        <v>134194.8</v>
       </c>
       <c r="F49" t="n">
-        <v>80497.60000000001</v>
+        <v>174680.9</v>
       </c>
       <c r="G49" t="n">
-        <v>12879.6</v>
-      </c>
-      <c r="H49" t="n">
-        <v>6439.8</v>
-      </c>
+        <v>29657.9</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>160995.1</v>
+        <v>367053.71</v>
       </c>
       <c r="J49" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K49" t="n">
-        <v>50</v>
-      </c>
-      <c r="L49" t="n">
-        <v>5.8</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3019,51 +2788,47 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2020</v>
       </c>
       <c r="D50" t="n">
-        <v>12394.8</v>
+        <v>9035.799999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>34705.4</v>
+        <v>27971.4</v>
       </c>
       <c r="F50" t="n">
-        <v>61974</v>
+        <v>59315.6</v>
       </c>
       <c r="G50" t="n">
-        <v>9915.799999999999</v>
-      </c>
-      <c r="H50" t="n">
-        <v>4958</v>
-      </c>
+        <v>7776.2</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>123948</v>
+        <v>104098.9</v>
       </c>
       <c r="J50" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K50" t="n">
-        <v>50</v>
-      </c>
-      <c r="L50" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3071,51 +2836,47 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2021</v>
       </c>
       <c r="D51" t="n">
-        <v>14878.1</v>
+        <v>11424.4</v>
       </c>
       <c r="E51" t="n">
-        <v>41658.6</v>
+        <v>35365.7</v>
       </c>
       <c r="F51" t="n">
-        <v>74390.39999999999</v>
+        <v>74995.89999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>11902.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>5951.2</v>
-      </c>
+        <v>9831.9</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>148780.8</v>
+        <v>131617.96</v>
       </c>
       <c r="J51" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K51" t="n">
-        <v>50</v>
-      </c>
-      <c r="L51" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3123,51 +2884,47 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2022</v>
       </c>
       <c r="D52" t="n">
-        <v>17955.8</v>
+        <v>12588.3</v>
       </c>
       <c r="E52" t="n">
-        <v>50276.4</v>
+        <v>38968.5</v>
       </c>
       <c r="F52" t="n">
-        <v>89779.2</v>
+        <v>82635.8</v>
       </c>
       <c r="G52" t="n">
-        <v>14364.7</v>
-      </c>
-      <c r="H52" t="n">
-        <v>7182.3</v>
-      </c>
+        <v>10833.4</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>179558.4</v>
+        <v>145026.05</v>
       </c>
       <c r="J52" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K52" t="n">
-        <v>50</v>
-      </c>
-      <c r="L52" t="n">
-        <v>7.3</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3175,51 +2932,47 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2023</v>
       </c>
       <c r="D53" t="n">
-        <v>20160.2</v>
+        <v>9867.5</v>
       </c>
       <c r="E53" t="n">
-        <v>56448.7</v>
+        <v>46932.3</v>
       </c>
       <c r="F53" t="n">
-        <v>100801.2</v>
+        <v>85107.2</v>
       </c>
       <c r="G53" t="n">
-        <v>16128.2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>8064.1</v>
-      </c>
+        <v>12272.7</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>201602.4</v>
+        <v>154179.63</v>
       </c>
       <c r="J53" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K53" t="n">
-        <v>50</v>
-      </c>
-      <c r="L53" t="n">
-        <v>7.3</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3227,51 +2980,47 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2024</v>
       </c>
       <c r="D54" t="n">
-        <v>20659.2</v>
+        <v>12342.7</v>
       </c>
       <c r="E54" t="n">
-        <v>57845.8</v>
+        <v>58001.3</v>
       </c>
       <c r="F54" t="n">
-        <v>103296</v>
+        <v>75500.10000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>16527.4</v>
-      </c>
-      <c r="H54" t="n">
-        <v>8263.6</v>
-      </c>
+        <v>12818.7</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>206592</v>
+        <v>158646.91</v>
       </c>
       <c r="J54" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K54" t="n">
-        <v>50</v>
-      </c>
-      <c r="L54" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3279,51 +3028,47 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2025</v>
       </c>
       <c r="D55" t="n">
-        <v>23027.5</v>
+        <v>14328.9</v>
       </c>
       <c r="E55" t="n">
-        <v>64477.1</v>
+        <v>67334.8</v>
       </c>
       <c r="F55" t="n">
-        <v>115137.6</v>
+        <v>87649.39999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>18422</v>
-      </c>
-      <c r="H55" t="n">
-        <v>9211</v>
-      </c>
+        <v>14881.4</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>230275.2</v>
+        <v>184176.05</v>
       </c>
       <c r="J55" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K55" t="n">
-        <v>50</v>
-      </c>
-      <c r="L55" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3331,51 +3076,47 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2020</v>
       </c>
       <c r="D56" t="n">
-        <v>6327.7</v>
+        <v>16562</v>
       </c>
       <c r="E56" t="n">
-        <v>17717.6</v>
+        <v>51269.7</v>
       </c>
       <c r="F56" t="n">
-        <v>31638.6</v>
+        <v>108721.5</v>
       </c>
       <c r="G56" t="n">
-        <v>5062.2</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2531.1</v>
-      </c>
+        <v>14253.2</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>63277.2</v>
+        <v>190806.47</v>
       </c>
       <c r="J56" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K56" t="n">
-        <v>50</v>
-      </c>
-      <c r="L56" t="n">
-        <v>6.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3383,51 +3124,47 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2021</v>
       </c>
       <c r="D57" t="n">
-        <v>7801.9</v>
+        <v>19397.6</v>
       </c>
       <c r="E57" t="n">
-        <v>21845.4</v>
+        <v>60047.6</v>
       </c>
       <c r="F57" t="n">
-        <v>39009.6</v>
+        <v>127335.8</v>
       </c>
       <c r="G57" t="n">
-        <v>6241.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>3120.8</v>
-      </c>
+        <v>16693.5</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>78019.2</v>
+        <v>223474.47</v>
       </c>
       <c r="J57" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K57" t="n">
-        <v>50</v>
-      </c>
-      <c r="L57" t="n">
-        <v>6.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3435,51 +3172,47 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2022</v>
       </c>
       <c r="D58" t="n">
-        <v>9737.299999999999</v>
+        <v>28316.1</v>
       </c>
       <c r="E58" t="n">
-        <v>27264.4</v>
+        <v>87655.89999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>48686.4</v>
+        <v>185881.5</v>
       </c>
       <c r="G58" t="n">
-        <v>7789.8</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3894.9</v>
-      </c>
+        <v>24368.8</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>97372.8</v>
+        <v>326222.31</v>
       </c>
       <c r="J58" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K58" t="n">
-        <v>50</v>
-      </c>
-      <c r="L58" t="n">
-        <v>7.9</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3487,51 +3220,47 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2023</v>
       </c>
       <c r="D59" t="n">
-        <v>10833.9</v>
+        <v>25398</v>
       </c>
       <c r="E59" t="n">
-        <v>30334.9</v>
+        <v>120799.2</v>
       </c>
       <c r="F59" t="n">
-        <v>54169.5</v>
+        <v>219057.6</v>
       </c>
       <c r="G59" t="n">
-        <v>8667.1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>4333.6</v>
-      </c>
+        <v>31588.7</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>108339</v>
+        <v>396843.5</v>
       </c>
       <c r="J59" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K59" t="n">
-        <v>50</v>
-      </c>
-      <c r="L59" t="n">
-        <v>7.9</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3539,51 +3268,47 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D60" t="n">
-        <v>18819</v>
+        <v>35951.2</v>
       </c>
       <c r="E60" t="n">
-        <v>52693.2</v>
+        <v>168942.8</v>
       </c>
       <c r="F60" t="n">
-        <v>94095</v>
+        <v>219912.2</v>
       </c>
       <c r="G60" t="n">
-        <v>15055.2</v>
-      </c>
-      <c r="H60" t="n">
-        <v>7527.6</v>
-      </c>
+        <v>37337.5</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>188190</v>
+        <v>462097.42</v>
       </c>
       <c r="J60" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K60" t="n">
-        <v>50</v>
-      </c>
-      <c r="L60" t="n">
-        <v>6.1</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3591,51 +3316,47 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D61" t="n">
-        <v>22399.1</v>
+        <v>40815.9</v>
       </c>
       <c r="E61" t="n">
-        <v>62717.5</v>
+        <v>191803.3</v>
       </c>
       <c r="F61" t="n">
-        <v>111995.6</v>
+        <v>249669.5</v>
       </c>
       <c r="G61" t="n">
-        <v>17919.3</v>
-      </c>
-      <c r="H61" t="n">
-        <v>8959.700000000001</v>
-      </c>
+        <v>42389.8</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>223991.2</v>
+        <v>524625.96</v>
       </c>
       <c r="J61" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K61" t="n">
-        <v>50</v>
-      </c>
-      <c r="L61" t="n">
-        <v>6.1</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3643,51 +3364,47 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D62" t="n">
-        <v>26790.8</v>
+        <v>12284.8</v>
       </c>
       <c r="E62" t="n">
-        <v>75014.10000000001</v>
+        <v>38029.2</v>
       </c>
       <c r="F62" t="n">
-        <v>133953.8</v>
+        <v>80644</v>
       </c>
       <c r="G62" t="n">
-        <v>21432.6</v>
-      </c>
-      <c r="H62" t="n">
-        <v>10716.2</v>
-      </c>
+        <v>10572.3</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>267907.5</v>
+        <v>141530.38</v>
       </c>
       <c r="J62" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K62" t="n">
-        <v>50</v>
-      </c>
-      <c r="L62" t="n">
-        <v>7.9</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3695,51 +3412,47 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D63" t="n">
-        <v>31062</v>
+        <v>14132.2</v>
       </c>
       <c r="E63" t="n">
-        <v>86973.60000000001</v>
+        <v>43748</v>
       </c>
       <c r="F63" t="n">
-        <v>155310</v>
+        <v>92771.10000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>24849.6</v>
-      </c>
-      <c r="H63" t="n">
-        <v>12424.8</v>
-      </c>
+        <v>12162.2</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>310620</v>
+        <v>162813.38</v>
       </c>
       <c r="J63" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K63" t="n">
-        <v>50</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7.9</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3747,51 +3460,47 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D64" t="n">
-        <v>32855.6</v>
+        <v>17019.4</v>
       </c>
       <c r="E64" t="n">
-        <v>91995.7</v>
+        <v>52685.7</v>
       </c>
       <c r="F64" t="n">
-        <v>164278.1</v>
+        <v>111724.2</v>
       </c>
       <c r="G64" t="n">
-        <v>26284.5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>13142.3</v>
-      </c>
+        <v>14646.9</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>328556.2</v>
+        <v>196076.15</v>
       </c>
       <c r="J64" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
-      </c>
-      <c r="L64" t="n">
-        <v>6.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3799,51 +3508,47 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D65" t="n">
-        <v>35973</v>
+        <v>15648.9</v>
       </c>
       <c r="E65" t="n">
-        <v>100724.4</v>
+        <v>74430.10000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>179865</v>
+        <v>134971.7</v>
       </c>
       <c r="G65" t="n">
-        <v>28778.4</v>
-      </c>
-      <c r="H65" t="n">
-        <v>14389.2</v>
-      </c>
+        <v>19463.3</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>359730</v>
+        <v>244514</v>
       </c>
       <c r="J65" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K65" t="n">
-        <v>50</v>
-      </c>
-      <c r="L65" t="n">
-        <v>6.1</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3851,51 +3556,47 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D66" t="n">
-        <v>8079.1</v>
+        <v>22023.9</v>
       </c>
       <c r="E66" t="n">
-        <v>22621.3</v>
+        <v>103495.4</v>
       </c>
       <c r="F66" t="n">
-        <v>40395.2</v>
+        <v>134719.6</v>
       </c>
       <c r="G66" t="n">
-        <v>6463.2</v>
-      </c>
-      <c r="H66" t="n">
-        <v>3231.7</v>
-      </c>
+        <v>22873.2</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>80790.5</v>
+        <v>283083.75</v>
       </c>
       <c r="J66" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
-      </c>
-      <c r="L66" t="n">
-        <v>5.7</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3903,51 +3604,47 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D67" t="n">
-        <v>9762.6</v>
+        <v>25836.8</v>
       </c>
       <c r="E67" t="n">
-        <v>27335.4</v>
+        <v>121413</v>
       </c>
       <c r="F67" t="n">
-        <v>48813.2</v>
+        <v>158042.8</v>
       </c>
       <c r="G67" t="n">
-        <v>7810.1</v>
-      </c>
-      <c r="H67" t="n">
-        <v>3905.1</v>
-      </c>
+        <v>26833.1</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>97626.39999999999</v>
+        <v>332092.37</v>
       </c>
       <c r="J67" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K67" t="n">
-        <v>50</v>
-      </c>
-      <c r="L67" t="n">
-        <v>5.7</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -3955,51 +3652,47 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D68" t="n">
-        <v>12172.2</v>
+        <v>17501.5</v>
       </c>
       <c r="E68" t="n">
-        <v>34082.2</v>
+        <v>54178.1</v>
       </c>
       <c r="F68" t="n">
-        <v>60861.1</v>
+        <v>114889</v>
       </c>
       <c r="G68" t="n">
-        <v>9737.799999999999</v>
-      </c>
-      <c r="H68" t="n">
-        <v>4868.8</v>
-      </c>
+        <v>15061.8</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>121722.1</v>
+        <v>201630.38</v>
       </c>
       <c r="J68" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
-      </c>
-      <c r="L68" t="n">
-        <v>7.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4007,51 +3700,47 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D69" t="n">
-        <v>13779.6</v>
+        <v>24913.8</v>
       </c>
       <c r="E69" t="n">
-        <v>38582.9</v>
+        <v>77123.60000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>68897.89999999999</v>
+        <v>163546.7</v>
       </c>
       <c r="G69" t="n">
-        <v>11023.7</v>
-      </c>
-      <c r="H69" t="n">
-        <v>5511.8</v>
-      </c>
+        <v>21440.8</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>137795.9</v>
+        <v>287024.8</v>
       </c>
       <c r="J69" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
-      </c>
-      <c r="L69" t="n">
-        <v>7.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4059,51 +3748,47 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D70" t="n">
-        <v>14182</v>
+        <v>25163.7</v>
       </c>
       <c r="E70" t="n">
-        <v>39709.6</v>
+        <v>77897.2</v>
       </c>
       <c r="F70" t="n">
-        <v>70910</v>
+        <v>165187.3</v>
       </c>
       <c r="G70" t="n">
-        <v>11345.6</v>
-      </c>
-      <c r="H70" t="n">
-        <v>5672.8</v>
-      </c>
+        <v>21655.8</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>141820</v>
+        <v>289903.96</v>
       </c>
       <c r="J70" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K70" t="n">
-        <v>50</v>
-      </c>
-      <c r="L70" t="n">
-        <v>5.7</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4111,51 +3796,47 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D71" t="n">
-        <v>15493.3</v>
+        <v>19927.5</v>
       </c>
       <c r="E71" t="n">
-        <v>43381.2</v>
+        <v>94780.39999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>77466.39999999999</v>
+        <v>171875.1</v>
       </c>
       <c r="G71" t="n">
-        <v>12394.6</v>
-      </c>
-      <c r="H71" t="n">
-        <v>6197.3</v>
-      </c>
+        <v>24784.9</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>154932.8</v>
+        <v>311367.92</v>
       </c>
       <c r="J71" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K71" t="n">
-        <v>50</v>
-      </c>
-      <c r="L71" t="n">
-        <v>5.7</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4163,51 +3844,47 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D72" t="n">
-        <v>15610.5</v>
+        <v>27548.7</v>
       </c>
       <c r="E72" t="n">
-        <v>43709.4</v>
+        <v>129457.8</v>
       </c>
       <c r="F72" t="n">
-        <v>78052.60000000001</v>
+        <v>168514.7</v>
       </c>
       <c r="G72" t="n">
-        <v>12488.4</v>
-      </c>
-      <c r="H72" t="n">
-        <v>6244.2</v>
-      </c>
+        <v>28611</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>156105.1</v>
+        <v>354096.86</v>
       </c>
       <c r="J72" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K72" t="n">
-        <v>50</v>
-      </c>
-      <c r="L72" t="n">
-        <v>6.3</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4215,51 +3892,47 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D73" t="n">
-        <v>18726.4</v>
+        <v>24823.3</v>
       </c>
       <c r="E73" t="n">
-        <v>52433.9</v>
+        <v>116650.5</v>
       </c>
       <c r="F73" t="n">
-        <v>93631.89999999999</v>
+        <v>151843.5</v>
       </c>
       <c r="G73" t="n">
-        <v>14981.1</v>
-      </c>
-      <c r="H73" t="n">
-        <v>7490.6</v>
-      </c>
+        <v>25780.5</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>187263.9</v>
+        <v>319065.9</v>
       </c>
       <c r="J73" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K73" t="n">
-        <v>50</v>
-      </c>
-      <c r="L73" t="n">
-        <v>6.3</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4267,51 +3940,47 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D74" t="n">
-        <v>22732.9</v>
+        <v>14440.2</v>
       </c>
       <c r="E74" t="n">
-        <v>63652</v>
+        <v>44701.5</v>
       </c>
       <c r="F74" t="n">
-        <v>113664.4</v>
+        <v>94793.10000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>18186.3</v>
-      </c>
-      <c r="H74" t="n">
-        <v>9093.1</v>
-      </c>
+        <v>12427.3</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>227328.7</v>
+        <v>166362.13</v>
       </c>
       <c r="J74" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K74" t="n">
-        <v>50</v>
-      </c>
-      <c r="L74" t="n">
-        <v>8.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4319,51 +3988,47 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D75" t="n">
-        <v>24902.6</v>
+        <v>15151.6</v>
       </c>
       <c r="E75" t="n">
-        <v>69727.39999999999</v>
+        <v>46903.7</v>
       </c>
       <c r="F75" t="n">
-        <v>124513.2</v>
+        <v>99463</v>
       </c>
       <c r="G75" t="n">
-        <v>19922.1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>9961.1</v>
-      </c>
+        <v>13039.5</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>249026.4</v>
+        <v>174557.7</v>
       </c>
       <c r="J75" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
-      </c>
-      <c r="L75" t="n">
-        <v>8.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4371,51 +4036,47 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D76" t="n">
-        <v>26632</v>
+        <v>16039.9</v>
       </c>
       <c r="E76" t="n">
-        <v>74569.60000000001</v>
+        <v>49653.4</v>
       </c>
       <c r="F76" t="n">
-        <v>133160</v>
+        <v>105294</v>
       </c>
       <c r="G76" t="n">
-        <v>21305.6</v>
-      </c>
-      <c r="H76" t="n">
-        <v>10652.7</v>
-      </c>
+        <v>13803.9</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>266319.9</v>
+        <v>184791.07</v>
       </c>
       <c r="J76" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
-      </c>
-      <c r="L76" t="n">
-        <v>6.3</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4423,51 +4084,47 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D77" t="n">
-        <v>28255.2</v>
+        <v>22682.5</v>
       </c>
       <c r="E77" t="n">
-        <v>79114.60000000001</v>
+        <v>107883.7</v>
       </c>
       <c r="F77" t="n">
-        <v>141276</v>
+        <v>195636.8</v>
       </c>
       <c r="G77" t="n">
-        <v>22604.2</v>
-      </c>
-      <c r="H77" t="n">
-        <v>11302</v>
-      </c>
+        <v>28211.4</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>282552</v>
+        <v>354414.42</v>
       </c>
       <c r="J77" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
-      </c>
-      <c r="L77" t="n">
-        <v>6.3</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4475,51 +4132,47 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D78" t="n">
-        <v>13657.2</v>
+        <v>31385.8</v>
       </c>
       <c r="E78" t="n">
-        <v>38240.2</v>
+        <v>147489.2</v>
       </c>
       <c r="F78" t="n">
-        <v>68286</v>
+        <v>191986.1</v>
       </c>
       <c r="G78" t="n">
-        <v>10925.8</v>
-      </c>
-      <c r="H78" t="n">
-        <v>5462.8</v>
-      </c>
+        <v>32596.1</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>136572</v>
+        <v>403416.96</v>
       </c>
       <c r="J78" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K78" t="n">
-        <v>50</v>
-      </c>
-      <c r="L78" t="n">
-        <v>5.8</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4527,51 +4180,47 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D79" t="n">
-        <v>17244.5</v>
+        <v>36748.6</v>
       </c>
       <c r="E79" t="n">
-        <v>48284.6</v>
+        <v>172690.2</v>
       </c>
       <c r="F79" t="n">
-        <v>86222.5</v>
+        <v>224790.2</v>
       </c>
       <c r="G79" t="n">
-        <v>13795.6</v>
-      </c>
-      <c r="H79" t="n">
-        <v>6897.8</v>
-      </c>
+        <v>38165.7</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>172445</v>
+        <v>472347.47</v>
       </c>
       <c r="J79" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K79" t="n">
-        <v>50</v>
-      </c>
-      <c r="L79" t="n">
-        <v>5.8</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4579,51 +4228,47 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D80" t="n">
-        <v>20184.7</v>
+        <v>11428.1</v>
       </c>
       <c r="E80" t="n">
-        <v>56517.2</v>
+        <v>35377.1</v>
       </c>
       <c r="F80" t="n">
-        <v>100923.5</v>
+        <v>75020.10000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>16147.8</v>
-      </c>
-      <c r="H80" t="n">
-        <v>8073.8</v>
-      </c>
+        <v>9835</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>201847</v>
+        <v>131660.37</v>
       </c>
       <c r="J80" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K80" t="n">
-        <v>50</v>
-      </c>
-      <c r="L80" t="n">
-        <v>7.6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4631,51 +4276,47 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D81" t="n">
-        <v>22739.7</v>
+        <v>14277.7</v>
       </c>
       <c r="E81" t="n">
-        <v>63671.2</v>
+        <v>44198.3</v>
       </c>
       <c r="F81" t="n">
-        <v>113698.6</v>
+        <v>93726</v>
       </c>
       <c r="G81" t="n">
-        <v>18191.8</v>
-      </c>
-      <c r="H81" t="n">
-        <v>9095.9</v>
-      </c>
+        <v>12287.3</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>227397.2</v>
+        <v>164489.29</v>
       </c>
       <c r="J81" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K81" t="n">
-        <v>50</v>
-      </c>
-      <c r="L81" t="n">
-        <v>7.6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4683,51 +4324,47 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D82" t="n">
-        <v>24664.6</v>
+        <v>16042.1</v>
       </c>
       <c r="E82" t="n">
-        <v>69060.89999999999</v>
+        <v>49660.4</v>
       </c>
       <c r="F82" t="n">
-        <v>123323.1</v>
+        <v>105308.8</v>
       </c>
       <c r="G82" t="n">
-        <v>19731.7</v>
-      </c>
-      <c r="H82" t="n">
-        <v>9865.799999999999</v>
-      </c>
+        <v>13805.8</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>246646.1</v>
+        <v>184817.11</v>
       </c>
       <c r="J82" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K82" t="n">
-        <v>50</v>
-      </c>
-      <c r="L82" t="n">
-        <v>5.8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4735,51 +4372,47 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D83" t="n">
-        <v>26706.5</v>
+        <v>13459.5</v>
       </c>
       <c r="E83" t="n">
-        <v>74778.2</v>
+        <v>64016.7</v>
       </c>
       <c r="F83" t="n">
-        <v>133532.5</v>
+        <v>116088.2</v>
       </c>
       <c r="G83" t="n">
-        <v>21365.2</v>
-      </c>
-      <c r="H83" t="n">
-        <v>10682.6</v>
-      </c>
+        <v>16740.3</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>267065</v>
+        <v>210304.69</v>
       </c>
       <c r="J83" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K83" t="n">
-        <v>50</v>
-      </c>
-      <c r="L83" t="n">
-        <v>5.8</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4787,51 +4420,47 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Civil Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D84" t="n">
-        <v>3435.2</v>
+        <v>17422.7</v>
       </c>
       <c r="E84" t="n">
-        <v>9618.6</v>
+        <v>81873.39999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>17176.1</v>
+        <v>106574.3</v>
       </c>
       <c r="G84" t="n">
-        <v>2748.2</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1374.1</v>
-      </c>
+        <v>18094.6</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>34352.2</v>
+        <v>223942.59</v>
       </c>
       <c r="J84" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K84" t="n">
-        <v>50</v>
-      </c>
-      <c r="L84" t="n">
-        <v>5.6</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4839,51 +4468,47 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Civil Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D85" t="n">
-        <v>4307.7</v>
+        <v>21856.1</v>
       </c>
       <c r="E85" t="n">
-        <v>12061.6</v>
+        <v>102706.7</v>
       </c>
       <c r="F85" t="n">
-        <v>21538.5</v>
+        <v>133692.9</v>
       </c>
       <c r="G85" t="n">
-        <v>3446.2</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1723</v>
-      </c>
+        <v>22698.9</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>43077</v>
+        <v>280926.47</v>
       </c>
       <c r="J85" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
-      </c>
-      <c r="L85" t="n">
-        <v>5.6</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4891,51 +4516,47 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Civil Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D86" t="n">
-        <v>5116.8</v>
+        <v>10367.5</v>
       </c>
       <c r="E86" t="n">
-        <v>14327</v>
+        <v>32094</v>
       </c>
       <c r="F86" t="n">
-        <v>25584</v>
+        <v>68057.8</v>
       </c>
       <c r="G86" t="n">
-        <v>4093.4</v>
-      </c>
-      <c r="H86" t="n">
-        <v>2046.8</v>
-      </c>
+        <v>8922.299999999999</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>51168</v>
+        <v>119441.61</v>
       </c>
       <c r="J86" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K86" t="n">
-        <v>50</v>
-      </c>
-      <c r="L86" t="n">
-        <v>7.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4943,51 +4564,47 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Civil Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D87" t="n">
-        <v>5687.3</v>
+        <v>13379.3</v>
       </c>
       <c r="E87" t="n">
-        <v>15924.5</v>
+        <v>41417.3</v>
       </c>
       <c r="F87" t="n">
-        <v>28436.6</v>
+        <v>87828.7</v>
       </c>
       <c r="G87" t="n">
-        <v>4549.9</v>
-      </c>
-      <c r="H87" t="n">
-        <v>2274.9</v>
-      </c>
+        <v>11514.2</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>56873.2</v>
+        <v>154139.51</v>
       </c>
       <c r="J87" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K87" t="n">
-        <v>50</v>
-      </c>
-      <c r="L87" t="n">
-        <v>7.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -4995,51 +4612,47 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CCBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Century Commercial Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D88" t="n">
-        <v>4767.5</v>
+        <v>13905.7</v>
       </c>
       <c r="E88" t="n">
-        <v>13348.9</v>
+        <v>43046.6</v>
       </c>
       <c r="F88" t="n">
-        <v>23837.4</v>
+        <v>91283.89999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>3814</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1907</v>
-      </c>
+        <v>11967.2</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>47674.8</v>
+        <v>160203.35</v>
       </c>
       <c r="J88" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K88" t="n">
-        <v>50</v>
-      </c>
-      <c r="L88" t="n">
-        <v>6.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5047,51 +4660,47 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CCBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Century Commercial Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D89" t="n">
-        <v>5885.9</v>
+        <v>11139.7</v>
       </c>
       <c r="E89" t="n">
-        <v>16480.6</v>
+        <v>52983.3</v>
       </c>
       <c r="F89" t="n">
-        <v>29429.6</v>
+        <v>96080</v>
       </c>
       <c r="G89" t="n">
-        <v>4708.7</v>
-      </c>
-      <c r="H89" t="n">
-        <v>2354.4</v>
-      </c>
+        <v>13855</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>58859.2</v>
+        <v>174058.04</v>
       </c>
       <c r="J89" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K89" t="n">
-        <v>50</v>
-      </c>
-      <c r="L89" t="n">
-        <v>6.4</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5099,51 +4708,47 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CCBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Century Commercial Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D90" t="n">
-        <v>6787</v>
+        <v>16428.3</v>
       </c>
       <c r="E90" t="n">
-        <v>19003.6</v>
+        <v>77200.2</v>
       </c>
       <c r="F90" t="n">
-        <v>33934.9</v>
+        <v>100491.2</v>
       </c>
       <c r="G90" t="n">
-        <v>5429.6</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2714.8</v>
-      </c>
+        <v>17061.8</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>67869.89999999999</v>
+        <v>211160.28</v>
       </c>
       <c r="J90" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K90" t="n">
-        <v>50</v>
-      </c>
-      <c r="L90" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5151,51 +4756,47 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CCBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Century Commercial Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D91" t="n">
-        <v>7869</v>
+        <v>20489.5</v>
       </c>
       <c r="E91" t="n">
-        <v>22033.3</v>
+        <v>96284.7</v>
       </c>
       <c r="F91" t="n">
-        <v>39345.2</v>
+        <v>125333.4</v>
       </c>
       <c r="G91" t="n">
-        <v>6295.2</v>
-      </c>
-      <c r="H91" t="n">
-        <v>3147.7</v>
-      </c>
+        <v>21279.5</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>78690.39999999999</v>
+        <v>263360.69</v>
       </c>
       <c r="J91" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K91" t="n">
-        <v>50</v>
-      </c>
-      <c r="L91" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5203,51 +4804,47 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>2020</v>
       </c>
       <c r="D92" t="n">
-        <v>10688.7</v>
+        <v>11174.7</v>
       </c>
       <c r="E92" t="n">
-        <v>29928.4</v>
+        <v>34592.6</v>
       </c>
       <c r="F92" t="n">
-        <v>53443.7</v>
+        <v>73356.5</v>
       </c>
       <c r="G92" t="n">
-        <v>8551</v>
-      </c>
-      <c r="H92" t="n">
-        <v>4275.5</v>
-      </c>
+        <v>9616.9</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>106887.3</v>
+        <v>128740.77</v>
       </c>
       <c r="J92" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
-      </c>
-      <c r="L92" t="n">
-        <v>6.2</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5255,51 +4852,47 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>2021</v>
       </c>
       <c r="D93" t="n">
-        <v>12887.1</v>
+        <v>14309</v>
       </c>
       <c r="E93" t="n">
-        <v>36083.9</v>
+        <v>44295.3</v>
       </c>
       <c r="F93" t="n">
-        <v>64435.5</v>
+        <v>93931.8</v>
       </c>
       <c r="G93" t="n">
-        <v>10309.7</v>
-      </c>
-      <c r="H93" t="n">
-        <v>5154.8</v>
-      </c>
+        <v>12314.3</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>128871</v>
+        <v>164850.5</v>
       </c>
       <c r="J93" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K93" t="n">
-        <v>50</v>
-      </c>
-      <c r="L93" t="n">
-        <v>6.2</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5307,51 +4900,47 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>2022</v>
       </c>
       <c r="D94" t="n">
-        <v>15798.2</v>
+        <v>15507</v>
       </c>
       <c r="E94" t="n">
-        <v>44235</v>
+        <v>48003.8</v>
       </c>
       <c r="F94" t="n">
-        <v>78991</v>
+        <v>101796</v>
       </c>
       <c r="G94" t="n">
-        <v>12638.6</v>
-      </c>
-      <c r="H94" t="n">
-        <v>6319.2</v>
-      </c>
+        <v>13345.3</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>157982</v>
+        <v>178652.18</v>
       </c>
       <c r="J94" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K94" t="n">
-        <v>50</v>
-      </c>
-      <c r="L94" t="n">
-        <v>8</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5359,51 +4948,47 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>2023</v>
       </c>
       <c r="D95" t="n">
-        <v>17453.7</v>
+        <v>18501.8</v>
       </c>
       <c r="E95" t="n">
-        <v>48870.4</v>
+        <v>87999.3</v>
       </c>
       <c r="F95" t="n">
-        <v>87268.5</v>
+        <v>159578.2</v>
       </c>
       <c r="G95" t="n">
-        <v>13963</v>
-      </c>
-      <c r="H95" t="n">
-        <v>6981.4</v>
-      </c>
+        <v>23011.6</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>174537</v>
+        <v>289090.93</v>
       </c>
       <c r="J95" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K95" t="n">
-        <v>50</v>
-      </c>
-      <c r="L95" t="n">
-        <v>8</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5411,51 +4996,47 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>2024</v>
       </c>
       <c r="D96" t="n">
-        <v>18915.7</v>
+        <v>23730</v>
       </c>
       <c r="E96" t="n">
-        <v>52964</v>
+        <v>111512.7</v>
       </c>
       <c r="F96" t="n">
-        <v>94578.5</v>
+        <v>145155.6</v>
       </c>
       <c r="G96" t="n">
-        <v>15132.6</v>
-      </c>
-      <c r="H96" t="n">
-        <v>7566.2</v>
-      </c>
+        <v>24645</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>189157</v>
+        <v>305012.85</v>
       </c>
       <c r="J96" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K96" t="n">
-        <v>50</v>
-      </c>
-      <c r="L96" t="n">
-        <v>6.2</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5463,51 +5044,47 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>2025</v>
       </c>
       <c r="D97" t="n">
-        <v>19730.6</v>
+        <v>26622.3</v>
       </c>
       <c r="E97" t="n">
-        <v>55245.5</v>
+        <v>125104.1</v>
       </c>
       <c r="F97" t="n">
-        <v>98652.8</v>
+        <v>162847.5</v>
       </c>
       <c r="G97" t="n">
-        <v>15784.4</v>
-      </c>
-      <c r="H97" t="n">
-        <v>7892.2</v>
-      </c>
+        <v>27648.8</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>197305.5</v>
+        <v>342188.54</v>
       </c>
       <c r="J97" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K97" t="n">
-        <v>50</v>
-      </c>
-      <c r="L97" t="n">
-        <v>6.2</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5515,51 +5092,47 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>2020</v>
       </c>
       <c r="D98" t="n">
-        <v>13461.1</v>
+        <v>20042.3</v>
       </c>
       <c r="E98" t="n">
-        <v>37691.1</v>
+        <v>62043.5</v>
       </c>
       <c r="F98" t="n">
-        <v>67305.60000000001</v>
+        <v>131568.3</v>
       </c>
       <c r="G98" t="n">
-        <v>10768.9</v>
-      </c>
-      <c r="H98" t="n">
-        <v>5384.5</v>
-      </c>
+        <v>17248.4</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>134611.2</v>
+        <v>230902.64</v>
       </c>
       <c r="J98" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K98" t="n">
-        <v>50</v>
-      </c>
-      <c r="L98" t="n">
-        <v>6.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5567,51 +5140,47 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>2021</v>
       </c>
       <c r="D99" t="n">
-        <v>16239.7</v>
+        <v>22901</v>
       </c>
       <c r="E99" t="n">
-        <v>45471.1</v>
+        <v>70892.89999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>81198.39999999999</v>
+        <v>150334.2</v>
       </c>
       <c r="G99" t="n">
-        <v>12991.8</v>
-      </c>
-      <c r="H99" t="n">
-        <v>6495.9</v>
-      </c>
+        <v>19708.6</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>162396.9</v>
+        <v>263836.77</v>
       </c>
       <c r="J99" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K99" t="n">
-        <v>50</v>
-      </c>
-      <c r="L99" t="n">
-        <v>6.1</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5619,51 +5188,47 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>2022</v>
       </c>
       <c r="D100" t="n">
-        <v>19557.5</v>
+        <v>22406.9</v>
       </c>
       <c r="E100" t="n">
-        <v>54760.9</v>
+        <v>69363.39999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>97787.2</v>
+        <v>147090.6</v>
       </c>
       <c r="G100" t="n">
-        <v>15646</v>
-      </c>
-      <c r="H100" t="n">
-        <v>7822.9</v>
-      </c>
+        <v>19283.4</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>195574.5</v>
+        <v>258144.3</v>
       </c>
       <c r="J100" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K100" t="n">
-        <v>50</v>
-      </c>
-      <c r="L100" t="n">
-        <v>7.9</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5671,51 +5236,47 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>2023</v>
       </c>
       <c r="D101" t="n">
-        <v>21740.9</v>
+        <v>20585.9</v>
       </c>
       <c r="E101" t="n">
-        <v>60874.6</v>
+        <v>97911.8</v>
       </c>
       <c r="F101" t="n">
-        <v>108704.7</v>
+        <v>177553.5</v>
       </c>
       <c r="G101" t="n">
-        <v>17392.8</v>
-      </c>
-      <c r="H101" t="n">
-        <v>8696.4</v>
-      </c>
+        <v>25603.7</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>217409.4</v>
+        <v>321654.94</v>
       </c>
       <c r="J101" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K101" t="n">
-        <v>50</v>
-      </c>
-      <c r="L101" t="n">
-        <v>7.9</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5723,51 +5284,47 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>2024</v>
       </c>
       <c r="D102" t="n">
-        <v>23281.3</v>
+        <v>33390.8</v>
       </c>
       <c r="E102" t="n">
-        <v>65187.6</v>
+        <v>156911</v>
       </c>
       <c r="F102" t="n">
-        <v>116406.4</v>
+        <v>204250.5</v>
       </c>
       <c r="G102" t="n">
-        <v>18625</v>
-      </c>
-      <c r="H102" t="n">
-        <v>9312.6</v>
-      </c>
+        <v>34678.4</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>232812.9</v>
+        <v>429187.76</v>
       </c>
       <c r="J102" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K102" t="n">
-        <v>50</v>
-      </c>
-      <c r="L102" t="n">
-        <v>6.1</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5775,51 +5332,47 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>2025</v>
       </c>
       <c r="D103" t="n">
-        <v>24580.8</v>
+        <v>38932.3</v>
       </c>
       <c r="E103" t="n">
-        <v>68826.2</v>
+        <v>182951.6</v>
       </c>
       <c r="F103" t="n">
-        <v>122904</v>
+        <v>238147.3</v>
       </c>
       <c r="G103" t="n">
-        <v>19664.6</v>
-      </c>
-      <c r="H103" t="n">
-        <v>9832.4</v>
-      </c>
+        <v>40433.5</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="n">
-        <v>245808</v>
+        <v>500414.68</v>
       </c>
       <c r="J103" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K103" t="n">
-        <v>50</v>
-      </c>
-      <c r="L103" t="n">
-        <v>6.1</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5827,51 +5380,47 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>2020</v>
       </c>
       <c r="D104" t="n">
-        <v>24624.2</v>
+        <v>9309.299999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>68947.7</v>
+        <v>28818.1</v>
       </c>
       <c r="F104" t="n">
-        <v>123120.9</v>
+        <v>61111.2</v>
       </c>
       <c r="G104" t="n">
-        <v>19699.4</v>
-      </c>
-      <c r="H104" t="n">
-        <v>9849.700000000001</v>
-      </c>
+        <v>8011.6</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>246241.9</v>
+        <v>107250.2</v>
       </c>
       <c r="J104" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K104" t="n">
-        <v>50</v>
-      </c>
-      <c r="L104" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5879,51 +5428,47 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>2021</v>
       </c>
       <c r="D105" t="n">
-        <v>31361.8</v>
+        <v>11147.4</v>
       </c>
       <c r="E105" t="n">
-        <v>87812.89999999999</v>
+        <v>34508</v>
       </c>
       <c r="F105" t="n">
-        <v>156808.8</v>
+        <v>73177.10000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>25089.4</v>
-      </c>
-      <c r="H105" t="n">
-        <v>12544.6</v>
-      </c>
+        <v>9593.4</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>313617.5</v>
+        <v>128425.87</v>
       </c>
       <c r="J105" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K105" t="n">
-        <v>50</v>
-      </c>
-      <c r="L105" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5931,51 +5476,47 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>2022</v>
       </c>
       <c r="D106" t="n">
-        <v>36690.5</v>
+        <v>13672.6</v>
       </c>
       <c r="E106" t="n">
-        <v>102733.4</v>
+        <v>42325.2</v>
       </c>
       <c r="F106" t="n">
-        <v>183452.5</v>
+        <v>89754.10000000001</v>
       </c>
       <c r="G106" t="n">
-        <v>29352.4</v>
-      </c>
-      <c r="H106" t="n">
-        <v>14676.1</v>
-      </c>
+        <v>11766.6</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>366904.9</v>
+        <v>157518.54</v>
       </c>
       <c r="J106" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K106" t="n">
-        <v>50</v>
-      </c>
-      <c r="L106" t="n">
-        <v>7.3</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -5983,51 +5524,47 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>2023</v>
       </c>
       <c r="D107" t="n">
-        <v>40591.6</v>
+        <v>11247.7</v>
       </c>
       <c r="E107" t="n">
-        <v>113656.5</v>
+        <v>53496.9</v>
       </c>
       <c r="F107" t="n">
-        <v>202958</v>
+        <v>97011.39999999999</v>
       </c>
       <c r="G107" t="n">
-        <v>32473.3</v>
-      </c>
-      <c r="H107" t="n">
-        <v>16236.6</v>
-      </c>
+        <v>13989.3</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="n">
-        <v>405916</v>
+        <v>175745.25</v>
       </c>
       <c r="J107" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K107" t="n">
-        <v>50</v>
-      </c>
-      <c r="L107" t="n">
-        <v>7.3</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6035,51 +5572,47 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>2024</v>
       </c>
       <c r="D108" t="n">
-        <v>45825.8</v>
+        <v>15341.9</v>
       </c>
       <c r="E108" t="n">
-        <v>128312.2</v>
+        <v>72095.2</v>
       </c>
       <c r="F108" t="n">
-        <v>229128.9</v>
+        <v>93846.10000000001</v>
       </c>
       <c r="G108" t="n">
-        <v>36660.6</v>
-      </c>
-      <c r="H108" t="n">
-        <v>18330.3</v>
-      </c>
+        <v>15933.5</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>458257.8</v>
+        <v>197197.07</v>
       </c>
       <c r="J108" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K108" t="n">
-        <v>50</v>
-      </c>
-      <c r="L108" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6087,51 +5620,47 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>2025</v>
       </c>
       <c r="D109" t="n">
-        <v>49782.8</v>
+        <v>17423.7</v>
       </c>
       <c r="E109" t="n">
-        <v>139391.7</v>
+        <v>81877.8</v>
       </c>
       <c r="F109" t="n">
-        <v>248913.8</v>
+        <v>106580</v>
       </c>
       <c r="G109" t="n">
-        <v>39826.2</v>
-      </c>
-      <c r="H109" t="n">
-        <v>19913</v>
-      </c>
+        <v>18095.5</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>497827.5</v>
+        <v>223954.68</v>
       </c>
       <c r="J109" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K109" t="n">
-        <v>50</v>
-      </c>
-      <c r="L109" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6139,51 +5668,47 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>2020</v>
       </c>
       <c r="D110" t="n">
-        <v>12741.3</v>
+        <v>9586.700000000001</v>
       </c>
       <c r="E110" t="n">
-        <v>35675.7</v>
+        <v>29676.8</v>
       </c>
       <c r="F110" t="n">
-        <v>63706.7</v>
+        <v>62932.1</v>
       </c>
       <c r="G110" t="n">
-        <v>10193.1</v>
-      </c>
-      <c r="H110" t="n">
-        <v>5096.5</v>
-      </c>
+        <v>8250.299999999999</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>127413.3</v>
+        <v>110445.87</v>
       </c>
       <c r="J110" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K110" t="n">
-        <v>50</v>
-      </c>
-      <c r="L110" t="n">
-        <v>5.6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6191,51 +5716,47 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>2021</v>
       </c>
       <c r="D111" t="n">
-        <v>15772.8</v>
+        <v>9221.5</v>
       </c>
       <c r="E111" t="n">
-        <v>44163.8</v>
+        <v>28546.3</v>
       </c>
       <c r="F111" t="n">
-        <v>78863.89999999999</v>
+        <v>60534.7</v>
       </c>
       <c r="G111" t="n">
-        <v>12618.2</v>
-      </c>
-      <c r="H111" t="n">
-        <v>6309</v>
-      </c>
+        <v>7936</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>157727.7</v>
+        <v>106238.47</v>
       </c>
       <c r="J111" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K111" t="n">
-        <v>50</v>
-      </c>
-      <c r="L111" t="n">
-        <v>5.6</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6243,51 +5764,47 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>2022</v>
       </c>
       <c r="D112" t="n">
-        <v>17788.8</v>
+        <v>10390.8</v>
       </c>
       <c r="E112" t="n">
-        <v>49808.6</v>
+        <v>32166.1</v>
       </c>
       <c r="F112" t="n">
-        <v>88944</v>
+        <v>68210.89999999999</v>
       </c>
       <c r="G112" t="n">
-        <v>14231</v>
-      </c>
-      <c r="H112" t="n">
-        <v>7115.6</v>
-      </c>
+        <v>8942.4</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>177888</v>
+        <v>119710.21</v>
       </c>
       <c r="J112" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K112" t="n">
-        <v>50</v>
-      </c>
-      <c r="L112" t="n">
-        <v>7.4</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6295,51 +5812,47 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>2023</v>
       </c>
       <c r="D113" t="n">
-        <v>21159.7</v>
+        <v>9653</v>
       </c>
       <c r="E113" t="n">
-        <v>59247</v>
+        <v>45912.2</v>
       </c>
       <c r="F113" t="n">
-        <v>105798.2</v>
+        <v>83257.3</v>
       </c>
       <c r="G113" t="n">
-        <v>16927.7</v>
-      </c>
-      <c r="H113" t="n">
-        <v>8463.9</v>
-      </c>
+        <v>12005.9</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>211596.5</v>
+        <v>150828.38</v>
       </c>
       <c r="J113" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K113" t="n">
-        <v>50</v>
-      </c>
-      <c r="L113" t="n">
-        <v>7.4</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6347,51 +5860,47 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>2024</v>
       </c>
       <c r="D114" t="n">
-        <v>21729.1</v>
+        <v>13655.1</v>
       </c>
       <c r="E114" t="n">
-        <v>60841.4</v>
+        <v>64168.2</v>
       </c>
       <c r="F114" t="n">
-        <v>108645.3</v>
+        <v>83527.5</v>
       </c>
       <c r="G114" t="n">
-        <v>17383.2</v>
-      </c>
-      <c r="H114" t="n">
-        <v>8691.6</v>
-      </c>
+        <v>14181.6</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>217290.6</v>
+        <v>175514.86</v>
       </c>
       <c r="J114" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K114" t="n">
-        <v>50</v>
-      </c>
-      <c r="L114" t="n">
-        <v>5.6</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6399,51 +5908,47 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>2025</v>
       </c>
       <c r="D115" t="n">
-        <v>23814.5</v>
+        <v>15529.1</v>
       </c>
       <c r="E115" t="n">
-        <v>66680.5</v>
+        <v>72975</v>
       </c>
       <c r="F115" t="n">
-        <v>119072.2</v>
+        <v>94991.3</v>
       </c>
       <c r="G115" t="n">
-        <v>19051.6</v>
-      </c>
-      <c r="H115" t="n">
-        <v>9525.700000000001</v>
-      </c>
+        <v>16128</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>238144.5</v>
+        <v>199603.44</v>
       </c>
       <c r="J115" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K115" t="n">
-        <v>50</v>
-      </c>
-      <c r="L115" t="n">
-        <v>5.6</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6451,51 +5956,47 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>2020</v>
       </c>
       <c r="D116" t="n">
-        <v>15241.8</v>
+        <v>12118.1</v>
       </c>
       <c r="E116" t="n">
-        <v>42677</v>
+        <v>37513.1</v>
       </c>
       <c r="F116" t="n">
-        <v>76208.89999999999</v>
+        <v>79549.5</v>
       </c>
       <c r="G116" t="n">
-        <v>12193.4</v>
-      </c>
-      <c r="H116" t="n">
-        <v>6096.6</v>
-      </c>
+        <v>10428.8</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>152417.7</v>
+        <v>139609.5</v>
       </c>
       <c r="J116" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K116" t="n">
-        <v>50</v>
-      </c>
-      <c r="L116" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6503,51 +6004,47 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>2021</v>
       </c>
       <c r="D117" t="n">
-        <v>18391.8</v>
+        <v>15704.2</v>
       </c>
       <c r="E117" t="n">
-        <v>51497.2</v>
+        <v>48614.3</v>
       </c>
       <c r="F117" t="n">
-        <v>91959.2</v>
+        <v>103090.5</v>
       </c>
       <c r="G117" t="n">
-        <v>14713.5</v>
-      </c>
-      <c r="H117" t="n">
-        <v>7356.7</v>
-      </c>
+        <v>13515</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>183918.4</v>
+        <v>180924.01</v>
       </c>
       <c r="J117" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K117" t="n">
-        <v>50</v>
-      </c>
-      <c r="L117" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6555,51 +6052,47 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>2022</v>
       </c>
       <c r="D118" t="n">
-        <v>22021.5</v>
+        <v>16626.6</v>
       </c>
       <c r="E118" t="n">
-        <v>61660.1</v>
+        <v>51469.7</v>
       </c>
       <c r="F118" t="n">
-        <v>110107.4</v>
+        <v>109145.6</v>
       </c>
       <c r="G118" t="n">
-        <v>17617.2</v>
-      </c>
-      <c r="H118" t="n">
-        <v>8808.5</v>
-      </c>
+        <v>14308.8</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>220214.7</v>
+        <v>191550.64</v>
       </c>
       <c r="J118" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K118" t="n">
-        <v>50</v>
-      </c>
-      <c r="L118" t="n">
-        <v>7.3</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6607,51 +6100,47 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>2023</v>
       </c>
       <c r="D119" t="n">
-        <v>25395.5</v>
+        <v>14313.9</v>
       </c>
       <c r="E119" t="n">
-        <v>71107.39999999999</v>
+        <v>68080.5</v>
       </c>
       <c r="F119" t="n">
-        <v>126977.6</v>
+        <v>123457.4</v>
       </c>
       <c r="G119" t="n">
-        <v>20316.4</v>
-      </c>
-      <c r="H119" t="n">
-        <v>10158.2</v>
-      </c>
+        <v>17802.9</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>253955.1</v>
+        <v>223654.67</v>
       </c>
       <c r="J119" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K119" t="n">
-        <v>50</v>
-      </c>
-      <c r="L119" t="n">
-        <v>7.3</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6659,51 +6148,47 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>2024</v>
       </c>
       <c r="D120" t="n">
-        <v>26705.1</v>
+        <v>18775.4</v>
       </c>
       <c r="E120" t="n">
-        <v>74774.3</v>
+        <v>88229.89999999999</v>
       </c>
       <c r="F120" t="n">
-        <v>133525.5</v>
+        <v>114848.5</v>
       </c>
       <c r="G120" t="n">
-        <v>21364.1</v>
-      </c>
-      <c r="H120" t="n">
-        <v>10682.1</v>
-      </c>
+        <v>19499.4</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>267051.1</v>
+        <v>241329.08</v>
       </c>
       <c r="J120" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K120" t="n">
-        <v>50</v>
-      </c>
-      <c r="L120" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6711,51 +6196,47 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>2025</v>
       </c>
       <c r="D121" t="n">
-        <v>28902.5</v>
+        <v>21809</v>
       </c>
       <c r="E121" t="n">
-        <v>80927.10000000001</v>
+        <v>102485.5</v>
       </c>
       <c r="F121" t="n">
-        <v>144512.7</v>
+        <v>133404.9</v>
       </c>
       <c r="G121" t="n">
-        <v>23122</v>
-      </c>
-      <c r="H121" t="n">
-        <v>11561.1</v>
-      </c>
+        <v>22650</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>289025.4</v>
+        <v>280321.37</v>
       </c>
       <c r="J121" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K121" t="n">
-        <v>50</v>
-      </c>
-      <c r="L121" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6763,51 +6244,47 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>2020</v>
       </c>
       <c r="D122" t="n">
-        <v>9431.700000000001</v>
+        <v>8247.799999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>26408.9</v>
+        <v>25532.1</v>
       </c>
       <c r="F122" t="n">
-        <v>47158.7</v>
+        <v>54142.9</v>
       </c>
       <c r="G122" t="n">
-        <v>7545.4</v>
-      </c>
-      <c r="H122" t="n">
-        <v>3772.7</v>
-      </c>
+        <v>7098.1</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>94317.39999999999</v>
+        <v>95020.84</v>
       </c>
       <c r="J122" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K122" t="n">
-        <v>50</v>
-      </c>
-      <c r="L122" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6815,51 +6292,47 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>2021</v>
       </c>
       <c r="D123" t="n">
-        <v>11168.4</v>
+        <v>7600.6</v>
       </c>
       <c r="E123" t="n">
-        <v>31271.5</v>
+        <v>23528.5</v>
       </c>
       <c r="F123" t="n">
-        <v>55842</v>
+        <v>49894.1</v>
       </c>
       <c r="G123" t="n">
-        <v>8934.700000000001</v>
-      </c>
-      <c r="H123" t="n">
-        <v>4467.4</v>
-      </c>
+        <v>6541</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>111684</v>
+        <v>87564.22</v>
       </c>
       <c r="J123" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K123" t="n">
-        <v>50</v>
-      </c>
-      <c r="L123" t="n">
-        <v>5.5</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6867,51 +6340,47 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>2022</v>
       </c>
       <c r="D124" t="n">
-        <v>13969.3</v>
+        <v>8135.1</v>
       </c>
       <c r="E124" t="n">
-        <v>39114.1</v>
+        <v>25183.1</v>
       </c>
       <c r="F124" t="n">
-        <v>69846.60000000001</v>
+        <v>53402.8</v>
       </c>
       <c r="G124" t="n">
-        <v>11175.5</v>
-      </c>
-      <c r="H124" t="n">
-        <v>5587.7</v>
-      </c>
+        <v>7001</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>139693.2</v>
+        <v>93721.92</v>
       </c>
       <c r="J124" t="n">
-        <v>38</v>
+        <v>35.55</v>
       </c>
       <c r="K124" t="n">
-        <v>50</v>
-      </c>
-      <c r="L124" t="n">
-        <v>7.3</v>
-      </c>
+        <v>56.98</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6919,51 +6388,47 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>2023</v>
       </c>
       <c r="D125" t="n">
-        <v>15650.1</v>
+        <v>7520.1</v>
       </c>
       <c r="E125" t="n">
-        <v>43820.3</v>
+        <v>35767.3</v>
       </c>
       <c r="F125" t="n">
-        <v>78250.60000000001</v>
+        <v>64860.5</v>
       </c>
       <c r="G125" t="n">
-        <v>12520.1</v>
-      </c>
-      <c r="H125" t="n">
-        <v>6260</v>
-      </c>
+        <v>9353.1</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>156501.1</v>
+        <v>117500.98</v>
       </c>
       <c r="J125" t="n">
-        <v>38</v>
+        <v>36.84</v>
       </c>
       <c r="K125" t="n">
-        <v>50</v>
-      </c>
-      <c r="L125" t="n">
-        <v>7.3</v>
-      </c>
+        <v>55.2</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -6971,51 +6436,47 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>2024</v>
       </c>
       <c r="D126" t="n">
-        <v>16724.2</v>
+        <v>8751.200000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>46827.8</v>
+        <v>41124.1</v>
       </c>
       <c r="F126" t="n">
-        <v>83621.10000000001</v>
+        <v>53531.1</v>
       </c>
       <c r="G126" t="n">
-        <v>13379.4</v>
-      </c>
-      <c r="H126" t="n">
-        <v>6689.6</v>
-      </c>
+        <v>9088.700000000001</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>167242.1</v>
+        <v>112483.89</v>
       </c>
       <c r="J126" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K126" t="n">
-        <v>50</v>
-      </c>
-      <c r="L126" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -7023,51 +6484,47 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>2025</v>
       </c>
       <c r="D127" t="n">
-        <v>18504</v>
+        <v>9751.4</v>
       </c>
       <c r="E127" t="n">
-        <v>51811.3</v>
+        <v>45823.9</v>
       </c>
       <c r="F127" t="n">
-        <v>92520.10000000001</v>
+        <v>59648.8</v>
       </c>
       <c r="G127" t="n">
-        <v>14803.2</v>
-      </c>
-      <c r="H127" t="n">
-        <v>7401.6</v>
-      </c>
+        <v>10127.4</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>185040.2</v>
+        <v>125338.85</v>
       </c>
       <c r="J127" t="n">
-        <v>38</v>
+        <v>44.34</v>
       </c>
       <c r="K127" t="n">
-        <v>50</v>
-      </c>
-      <c r="L127" t="n">
-        <v>5.5</v>
-      </c>
+        <v>47.59</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>NRB Deposit Profile</t>
@@ -7075,319 +6532,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Deposit structure in NPR Millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>NMB</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NMB Bank</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D128" t="n">
-        <v>13261</v>
-      </c>
-      <c r="E128" t="n">
-        <v>37130.9</v>
-      </c>
-      <c r="F128" t="n">
-        <v>66305.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>10608.8</v>
-      </c>
-      <c r="H128" t="n">
-        <v>5304.5</v>
-      </c>
-      <c r="I128" t="n">
-        <v>132610.4</v>
-      </c>
-      <c r="J128" t="n">
-        <v>38</v>
-      </c>
-      <c r="K128" t="n">
-        <v>50</v>
-      </c>
-      <c r="L128" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>NRB Deposit Profile</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>Deposit structure in NPR Millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>NMB</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>NMB Bank</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D129" t="n">
-        <v>16521.4</v>
-      </c>
-      <c r="E129" t="n">
-        <v>46260</v>
-      </c>
-      <c r="F129" t="n">
-        <v>82607.2</v>
-      </c>
-      <c r="G129" t="n">
-        <v>13217.2</v>
-      </c>
-      <c r="H129" t="n">
-        <v>6608.6</v>
-      </c>
-      <c r="I129" t="n">
-        <v>165214.4</v>
-      </c>
-      <c r="J129" t="n">
-        <v>38</v>
-      </c>
-      <c r="K129" t="n">
-        <v>50</v>
-      </c>
-      <c r="L129" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>NRB Deposit Profile</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>Deposit structure in NPR Millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>NMB</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NMB Bank</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D130" t="n">
-        <v>19017.4</v>
-      </c>
-      <c r="E130" t="n">
-        <v>53248.8</v>
-      </c>
-      <c r="F130" t="n">
-        <v>95087.2</v>
-      </c>
-      <c r="G130" t="n">
-        <v>15214</v>
-      </c>
-      <c r="H130" t="n">
-        <v>7607</v>
-      </c>
-      <c r="I130" t="n">
-        <v>190174.4</v>
-      </c>
-      <c r="J130" t="n">
-        <v>38</v>
-      </c>
-      <c r="K130" t="n">
-        <v>50</v>
-      </c>
-      <c r="L130" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>NRB Deposit Profile</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>Deposit structure in NPR Millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>NMB</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NMB Bank</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D131" t="n">
-        <v>21492.9</v>
-      </c>
-      <c r="E131" t="n">
-        <v>60180.1</v>
-      </c>
-      <c r="F131" t="n">
-        <v>107464.5</v>
-      </c>
-      <c r="G131" t="n">
-        <v>17194.3</v>
-      </c>
-      <c r="H131" t="n">
-        <v>8597.200000000001</v>
-      </c>
-      <c r="I131" t="n">
-        <v>214929</v>
-      </c>
-      <c r="J131" t="n">
-        <v>38</v>
-      </c>
-      <c r="K131" t="n">
-        <v>50</v>
-      </c>
-      <c r="L131" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>NRB Deposit Profile</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>Deposit structure in NPR Millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>NMB</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NMB Bank</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D132" t="n">
-        <v>22715.7</v>
-      </c>
-      <c r="E132" t="n">
-        <v>63603.9</v>
-      </c>
-      <c r="F132" t="n">
-        <v>113578.4</v>
-      </c>
-      <c r="G132" t="n">
-        <v>18172.5</v>
-      </c>
-      <c r="H132" t="n">
-        <v>9086.299999999999</v>
-      </c>
-      <c r="I132" t="n">
-        <v>227156.8</v>
-      </c>
-      <c r="J132" t="n">
-        <v>38</v>
-      </c>
-      <c r="K132" t="n">
-        <v>50</v>
-      </c>
-      <c r="L132" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>NRB Deposit Profile</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>Deposit structure in NPR Millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>NMB</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>NMB Bank</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D133" t="n">
-        <v>25309.4</v>
-      </c>
-      <c r="E133" t="n">
-        <v>70866.39999999999</v>
-      </c>
-      <c r="F133" t="n">
-        <v>126547.2</v>
-      </c>
-      <c r="G133" t="n">
-        <v>20247.6</v>
-      </c>
-      <c r="H133" t="n">
-        <v>10123.8</v>
-      </c>
-      <c r="I133" t="n">
-        <v>253094.4</v>
-      </c>
-      <c r="J133" t="n">
-        <v>38</v>
-      </c>
-      <c r="K133" t="n">
-        <v>50</v>
-      </c>
-      <c r="L133" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>NRB Deposit Profile</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>Deposit structure in NPR Millions</t>
+          <t>Deposit breakdown not extracted from PDFs</t>
         </is>
       </c>
     </row>
